--- a/artfynd/A 28438-2022 artfynd.xlsx
+++ b/artfynd/A 28438-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 28438-2022 artfynd.xlsx
+++ b/artfynd/A 28438-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106032029</v>
+        <v>106032965</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,43 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kopängsberget, Hedkärra, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542924.4184991239</v>
+        <v>543050</v>
       </c>
       <c r="R2" t="n">
-        <v>6648902.936008562</v>
+        <v>6648797</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,22 +759,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Talldominerad barrskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -809,22 +770,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Jacob Rudhe, Mårten Berglind, Carl Hanson, Henrik Berg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106032965</v>
+        <v>103800482</v>
       </c>
       <c r="B3" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,37 +788,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>112</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kopängsberget, Hedkärra, Vstm</t>
+          <t>Fagersta, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543050.5184088617</v>
+        <v>543025</v>
       </c>
       <c r="R3" t="n">
-        <v>6648797.266263111</v>
+        <v>6648896</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,22 +843,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,58 +859,48 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Talldominerad barrskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jacob Rudhe, Mårten Berglind, Carl Hanson, Henrik Berg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106032964</v>
+        <v>106032040</v>
       </c>
       <c r="B4" t="n">
-        <v>94160</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2590</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -973,10 +910,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543050.5184088617</v>
+        <v>542838</v>
       </c>
       <c r="R4" t="n">
-        <v>6648797.266263111</v>
+        <v>6648803</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,22 +940,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,9 +957,19 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Talldominerad barrskog</t>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1043,10 +980,442 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>106032964</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97394</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kopängsberget, Hedkärra, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>543050</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6648797</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Fagersta</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Fagersta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Talldominerad barrskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
           <t>Jacob Rudhe, Mårten Berglind, Carl Hanson, Henrik Berg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>106032029</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kopängsberget, Hedkärra, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>542924</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6648903</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Fagersta</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Fagersta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-07-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-07-28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>103801179</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Fagersta, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>542891</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6648866</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Fagersta</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Fagersta</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-09-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-09-28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>73770692</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kopängsberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>542925</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6648915</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Fagersta</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Fagersta</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2018-10-29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2018-10-29</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28438-2022 artfynd.xlsx
+++ b/artfynd/A 28438-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032965</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -872,6 +882,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103800482</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,6 +999,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032040</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,6 +1106,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032964</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106032029</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1310,6 +1340,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103801179</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1416,8 +1451,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73770692</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>